--- a/saidas/ordens_dia/ordem_dia_2026_08_07_executor_v5_5.xlsx
+++ b/saidas/ordens_dia/ordem_dia_2026_08_07_executor_v5_5.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE3"/>
+  <dimension ref="A1:DE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,26 +981,26 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1020,40 +1020,40 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1166</v>
+        <v>0.3607</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8519</v>
+        <v>0.7006</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.5357</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2496</v>
+        <v>1.3219</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7967</v>
+        <v>0.7869</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.039</v>
+        <v>0.2783</v>
       </c>
       <c r="R2" t="n">
         <v>443</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0304</v>
+        <v>0.5613</v>
       </c>
       <c r="T2" t="n">
-        <v>385</v>
+        <v>269</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7107</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1068</v>
+        <v>0.0776</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1067,49 +1067,49 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.8954</v>
+        <v>0.7464</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.7983</v>
+        <v>2.3324</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7097</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8954</v>
+        <v>0.7464</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1839</v>
+        <v>0.1319</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2286</v>
+        <v>0.1419</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3616</v>
+        <v>0.2427</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0399</v>
+        <v>0.0155</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.2165</v>
+        <v>0.4989</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.79</v>
+        <v>74.97</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.72</v>
+        <v>77.67</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0829</v>
+        <v>0.2289</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.128275</v>
+        <v>0.034882</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.122074</v>
+        <v>1.107236</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.21</v>
+        <v>10.72</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1124,25 +1124,25 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.034456</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
         <v>1.08</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.816703</v>
+        <v>0.97</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.111329</v>
+        <v>0.043256</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.1522</v>
+        <v>0.8064</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1166,7 +1166,11 @@
       <c r="BE2" t="n">
         <v>0</v>
       </c>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr">
         <is>
           <t>B</t>
@@ -1184,28 +1188,28 @@
         <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BP2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.7171717171717171</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS2" t="n">
         <v>1</v>
@@ -1215,59 +1219,59 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>exec_baixa</t>
+          <t>exec_bilateral</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>sem_edge</t>
+          <t>expansion_moderada</t>
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.5042</v>
+        <v>0.6612</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.7129</v>
+        <v>0.633</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.4399</v>
+        <v>0.531</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.4832765979561717</v>
+        <v>0.4728564098168937</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.6473258788685476</v>
+        <v>0.6497497742218987</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.6231809318200072</v>
+        <v>0.5405563528018854</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.6473258788685476</v>
+        <v>0.6497497742218987</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.7094017094017094</v>
+        <v>0.5477386934673367</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.5971223021582733</v>
+        <v>0.7730496453900709</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.6505376344086021</v>
+        <v>0.5943775100401606</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.7960526315789473</v>
+        <v>0.8604651162790697</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.8382352941176471</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.4042553191489361</v>
+        <v>0.3416149068322981</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>instabilidade_regressao</t>
+          <t>expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1290,10 +1294,10 @@
         <v>1</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.482</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.482</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1301,17 +1305,17 @@
       <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+          <t>Call delta~50 naked (ATM, máximo gamma)</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
+          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
@@ -1321,12 +1325,12 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.710 | spread_35_20: esp=+0.184 | spread_45_25: esp=+0.229 | spread_45_15: esp=+0.362</t>
+          <t>naked_30: esp=+0.634 | spread_35_20: esp=+0.132 | spread_45_25: esp=+0.142 | spread_45_15: esp=+0.243</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.895 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.746 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
@@ -1362,7 +1366,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1404,28 +1408,28 @@
         <v>193</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4168</v>
+        <v>0.4159</v>
       </c>
       <c r="M3" t="n">
         <v>0.6839</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3547</v>
+        <v>0.3529</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9006</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1115</v>
+        <v>0.1111</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1049</v>
+        <v>0.1047</v>
       </c>
       <c r="R3" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1306</v>
+        <v>0.1302</v>
       </c>
       <c r="T3" t="n">
         <v>405</v>
@@ -1434,7 +1438,7 @@
         <v>0.2293</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0482</v>
+        <v>0.0481</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1448,16 +1452,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.3108</v>
+        <v>0.3107</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.9711</v>
+        <v>0.9709</v>
       </c>
       <c r="AB3" t="n">
         <v>0.2283</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3108</v>
+        <v>0.3107</v>
       </c>
       <c r="AD3" t="n">
         <v>0.06370000000000001</v>
@@ -1466,31 +1470,31 @@
         <v>0.0877</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1372</v>
+        <v>0.1371</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0135</v>
+        <v>0.014</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2985</v>
+        <v>0.3393</v>
       </c>
       <c r="AI3" t="n">
-        <v>17.7</v>
+        <v>17.31</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17.15</v>
+        <v>16.75</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0956</v>
+        <v>0.0954</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.039926</v>
+        <v>-0.07148599999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.095515</v>
+        <v>1.144711</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.550000000000001</v>
+        <v>14.47</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -1520,10 +1524,10 @@
         <v>-1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.037621</v>
+        <v>0.039153</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.0613</v>
+        <v>1.8258</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1675,10 +1679,10 @@
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.5405</v>
+        <v>0.6088</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.5405</v>
+        <v>0.6088</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
@@ -1737,6 +1741,1153 @@
       <c r="DE3" t="inlineStr">
         <is>
           <t>Edge forte — aguardar dobrar o prêmio. Stop 50%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v5.5_executor_diario</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>alerta_executor_nivel_B</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>54</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.2606</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7846</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="R4" t="n">
+        <v>443</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="T4" t="n">
+        <v>385</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.7175</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>naked_45</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.9023</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.8196</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7165</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.9023</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.17893</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.087637</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.034456</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.816703</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.126914</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.4099</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>expansao</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.7171717171717171</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>exec_baixa</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>sem_edge</t>
+        </is>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.7129</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.4832765979561717</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.6473258788685476</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.6231809318200072</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.6473258788685476</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.7094017094017094</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.5971223021582733</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.6505376344086021</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.7960526315789473</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.8382352941176471</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.4042553191489361</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>instabilidade_regressao</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>threshold_por_ativo</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>RV_RANK</t>
+        </is>
+      </c>
+      <c r="CN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>OTM extremo sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>naked_30: esp=+0.717 | spread_35_20: esp=+0.184 | spread_45_25: esp=+0.229 | spread_45_15: esp=+0.362</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.902 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>80% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>40% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v5.5_executor_diario</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SBFG3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>alerta_executor_nivel_B</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.1786</v>
+      </c>
+      <c r="R5" t="n">
+        <v>443</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="T5" t="n">
+        <v>301</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>naked_45</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.0597</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.0668</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.047664</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.388515</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.286753</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.286753</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.058002</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.8218</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>expansao</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.9191919191919192</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>exec_baixa</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>expansion_moderada</t>
+        </is>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.5421</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.4339260142408751</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.5601962813967674</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0.6980220691000337</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.6980220691000337</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.6551724137931034</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.2435897435897436</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.2211538461538461</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.7166666666666667</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.5972222222222222</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>expansao_moderada_sem_exec_forte</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>threshold_por_ativo</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>OTM extremo sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>naked_30: esp=+0.060 | spread_35_20: esp=+0.067 | spread_45_25: esp=+0.079 | spread_45_15: esp=+0.115</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.129 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>80% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>40% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v5.5_executor_diario</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>alerta_executor_nivel_B</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>150</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.8581</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.0526</v>
+      </c>
+      <c r="R6" t="n">
+        <v>443</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.0404</v>
+      </c>
+      <c r="T6" t="n">
+        <v>340</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>naked_45</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.4632</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.083866</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.073351</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.101806</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.096987</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.8647</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>neutro_zona_cinza</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>exec_bilateral</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>expansion_moderada</t>
+        </is>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.6101</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.4918065430296099</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.6169490402740937</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.5467965898645156</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.6169490402740937</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.4594594594594595</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>expansao_moderada_sem_exec_forte</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>threshold_por_ativo</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>RV_RANK</t>
+        </is>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.5022</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.5022</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>OTM extremo sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>naked_30: esp=+0.137 | spread_35_20: esp=+0.015 | spread_45_25: esp=+0.002 | spread_45_15: esp=+0.030</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.148 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>80% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>40% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
         </is>
       </c>
     </row>
@@ -1844,7 +2995,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1853,7 +3004,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46233</v>
+        <v>46227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1866,57 +3017,57 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>5.34</v>
+        <v>11.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.55</v>
+        <v>10.76</v>
       </c>
       <c r="J2" t="n">
-        <v>-14.79</v>
+        <v>-5.61</v>
       </c>
       <c r="K2" t="n">
-        <v>1.259</v>
+        <v>0.824</v>
       </c>
       <c r="L2" t="n">
         <v>0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>0.769</v>
+        <v>0.334</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.208</v>
+        <v>1.489</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1068</v>
+        <v>-0.0842</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>M=1.26 ≥ BE+alvo=0.79 | lucro≈+0.77DP</t>
+          <t>M=0.82 ≥ BE+alvo=0.79 | lucro≈+0.33DP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NO LUCRO (segurar)</t>
+          <t>REALIZAR LUCRO</t>
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1929,61 +3080,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>11.4</v>
+        <v>5.34</v>
       </c>
       <c r="I3" t="n">
-        <v>11.02</v>
+        <v>4.52</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.33</v>
+        <v>-15.36</v>
       </c>
       <c r="K3" t="n">
-        <v>0.523</v>
+        <v>1.342</v>
       </c>
       <c r="L3" t="n">
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.033</v>
+        <v>0.852</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.014</v>
+        <v>1.307</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.111</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>M=0.52 ≥ BE=0.49 mas &lt; alvo | lucro≈+0.03DP — trailing</t>
+          <t>M=1.34 ≥ BE+alvo=0.79 | lucro≈+0.85DP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRSR6</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SINAL FRACO (reverter)</t>
+          <t>NO LUCRO (segurar)</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1998,51 +3149,51 @@
         <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>14.38</v>
+        <v>17.7</v>
       </c>
       <c r="I4" t="n">
-        <v>14.01</v>
+        <v>17.31</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.57</v>
+        <v>-2.2</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.543</v>
+        <v>0.581</v>
       </c>
       <c r="L4" t="n">
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.32</v>
+        <v>0.091</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.229</v>
+        <v>1.826</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0095</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>razao=0.23 &lt; 0.6 | M=-0.54 — ativo foi contra, tese falhou</t>
+          <t>M=0.58 ≥ BE=0.49 mas &lt; alvo | lucro≈+0.09DP — trailing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SINAL FRACO (reverter)</t>
+          <t>NO LUCRO (segurar)</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46227</v>
+        <v>46240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2055,111 +3206,111 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>20.7</v>
+        <v>0.79</v>
       </c>
       <c r="I5" t="n">
-        <v>21.83</v>
+        <v>0.72</v>
       </c>
       <c r="J5" t="n">
-        <v>5.46</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.32</v>
+        <v>0.2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.535</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0306</v>
+        <v>-0.1789</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>razao=0.54 &lt; 0.6 | M=-0.39 — ativo foi contra, tese falhou</t>
+          <t>M=0.69 ≥ BE=0.49 mas &lt; alvo | lucro≈+0.20DP — trailing</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SINAL FRACO (reverter)</t>
+          <t>SINAL INVERTIDO</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compra CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>13.61</v>
+        <v>20.7</v>
       </c>
       <c r="I6" t="n">
-        <v>13.51</v>
+        <v>21.67</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.73</v>
+        <v>4.69</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.273</v>
+        <v>-0.308</v>
       </c>
       <c r="L6" t="n">
-        <v>0.425</v>
+        <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.255</v>
+        <v>-0.32</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09</v>
+        <v>0.603</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0037</v>
+        <v>0.0343</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>razao=0.09 &lt; 0.6 | M=-0.27 — ativo foi contra, tese falhou</t>
+          <t>Modelo virou CALL | M=-0.31 | razao=0.60</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>BRSR6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2168,11 +3319,11 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2181,22 +3332,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>7.94</v>
+        <v>14.38</v>
       </c>
       <c r="I7" t="n">
-        <v>8.24</v>
+        <v>13.75</v>
       </c>
       <c r="J7" t="n">
-        <v>3.78</v>
+        <v>-4.38</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.174</v>
+        <v>-0.783</v>
       </c>
       <c r="L7" t="n">
         <v>0.49</v>
@@ -2208,160 +3359,160 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.242</v>
+        <v>0.31</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0151</v>
+        <v>-0.0134</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>razao=0.24 &lt; 0.6 | M=-0.17 — ativo foi contra, tese falhou</t>
+          <t>razao=0.31 &lt; 0.6 | M=-0.78 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MANTER</t>
+          <t>SINAL FRACO (reverter)</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46240</v>
+        <v>46221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>17.7</v>
+        <v>13.61</v>
       </c>
       <c r="I8" t="n">
-        <v>17.7</v>
+        <v>13.21</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>0.234</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.49</v>
+        <v>0.425</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.256</v>
+        <v>-0.255</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.061</v>
+        <v>0.317</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0399</v>
+        <v>-0.0139</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>M=0.23 | razao=1.06 | 0/20d</t>
+          <t>razao=0.32 &lt; 0.6 | M=-0.57 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>PETR3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MANTER</t>
+          <t>SINAL FRACO (segurar)</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46240</v>
+        <v>46219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>naked_30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>44.64</v>
       </c>
       <c r="I9" t="n">
-        <v>0.79</v>
+        <v>45.69</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="K9" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.181</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.237</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.253</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.152</v>
-      </c>
       <c r="P9" t="n">
-        <v>-0.1283</v>
+        <v>0.0134</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>M=0.24 | razao=1.15 | 0/20d</t>
+          <t>razao=0.24 &lt; 0.6 | M=0.14 — movimento OK, modelo ruidoso</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GGBR4</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MANTER</t>
+          <t>SINAL FRACO (segurar)</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2370,48 +3521,48 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>26.31</v>
+        <v>7.94</v>
       </c>
       <c r="I10" t="n">
-        <v>25.65</v>
+        <v>7.96</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.51</v>
+        <v>0.25</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.465</v>
+        <v>0.181</v>
       </c>
       <c r="L10" t="n">
         <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.32</v>
+        <v>-0.309</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.296</v>
+        <v>0.169</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1097</v>
+        <v>-0.0113</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>M=-0.46 | razao=2.30 | 1/20d</t>
+          <t>razao=0.17 &lt; 0.6 | M=0.18 — movimento OK, modelo ruidoso</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOAU4</t>
+          <t>GGBR4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2433,22 +3584,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>11.53</v>
+        <v>26.31</v>
       </c>
       <c r="I11" t="n">
-        <v>11.2</v>
+        <v>25.05</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.86</v>
+        <v>-4.79</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.496</v>
+        <v>-0.698</v>
       </c>
       <c r="L11" t="n">
         <v>0.49</v>
@@ -2460,21 +3611,21 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.894</v>
+        <v>1.593</v>
       </c>
       <c r="P11" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>M=-0.50 | razao=1.89 | 1/20d</t>
+          <t>M=-0.70 | razao=1.59 | 2/20d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PETR3</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2483,7 +3634,7 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46219</v>
+        <v>46239</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2492,45 +3643,45 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>naked_30</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>44.64</v>
+        <v>11.53</v>
       </c>
       <c r="I12" t="n">
-        <v>47.31</v>
+        <v>11.01</v>
       </c>
       <c r="J12" t="n">
-        <v>5.98</v>
+        <v>-4.51</v>
       </c>
       <c r="K12" t="n">
-        <v>0.62</v>
+        <v>-0.694</v>
       </c>
       <c r="L12" t="n">
-        <v>0.751</v>
+        <v>0.49</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.131</v>
+        <v>-0.32</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.644</v>
+        <v>1.644</v>
       </c>
       <c r="P12" t="n">
-        <v>0.032</v>
+        <v>0.0823</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>M=0.62 | razao=0.64 | 15/20d</t>
+          <t>M=-0.69 | razao=1.64 | 2/20d</t>
         </is>
       </c>
     </row>
@@ -2568,32 +3719,32 @@
         <v>9.359999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>9.140000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.35</v>
+        <v>-2.03</v>
       </c>
       <c r="K13" t="n">
-        <v>0.457</v>
+        <v>0.424</v>
       </c>
       <c r="L13" t="n">
         <v>0.49</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.033</v>
+        <v>-0.066</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.615</v>
+        <v>0.822</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0359</v>
+        <v>-0.0477</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>M=0.46 | razao=0.62 | 8/20d</t>
+          <t>M=0.42 | razao=0.82 | 8/20d</t>
         </is>
       </c>
     </row>
@@ -2622,22 +3773,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" t="n">
         <v>76.66</v>
       </c>
       <c r="I14" t="n">
-        <v>75.39</v>
+        <v>74.97</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.66</v>
+        <v>-2.2</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.38</v>
+        <v>-0.469</v>
       </c>
       <c r="L14" t="n">
         <v>0.49</v>
@@ -2649,14 +3800,14 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.746</v>
+        <v>0.806</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0331</v>
+        <v>0.0349</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>M=-0.38 | razao=0.75 | 1/20d</t>
+          <t>M=-0.47 | razao=0.81 | 2/20d</t>
         </is>
       </c>
     </row>
@@ -2671,7 +3822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,19 +3935,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2165</v>
+        <v>0.4989</v>
       </c>
       <c r="D2" t="n">
-        <v>1.122074</v>
+        <v>1.107236</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2804,7 +3955,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7107</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2813,7 +3964,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2838,17 +3989,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+          <t>Call delta~50 naked (ATM, máximo gamma)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
+          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2858,17 +4009,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.895 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.746 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.0399</v>
+        <v>0.0155</v>
       </c>
       <c r="S2" t="n">
-        <v>63.3</v>
+        <v>24.6</v>
       </c>
       <c r="T2" t="n">
-        <v>71.09999999999999</v>
+        <v>27.2</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -2888,10 +4039,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2985</v>
+        <v>0.3393</v>
       </c>
       <c r="D3" t="n">
-        <v>1.095515</v>
+        <v>1.144711</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2957,15 +4108,300 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.0135</v>
+        <v>0.014</v>
       </c>
       <c r="S3" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="T3" t="n">
-        <v>23.5</v>
+        <v>25.4</v>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.087637</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7175</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>80% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>40% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>OTM extremo sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.902 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="S4" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SBFG3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.388515</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>80% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>40% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>OTM extremo sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.129 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="S5" t="n">
+        <v>33</v>
+      </c>
+      <c r="T5" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.073351</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>80% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>40% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>OTM extremo sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.148 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="S6" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
         </is>
@@ -3529,7 +4965,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3555,14 +4991,14 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>vol_live_sem_expansao</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>56</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1212</v>
+        <v>0.121</v>
       </c>
       <c r="L2" t="n">
         <v>0.2321</v>
@@ -3577,16 +5013,16 @@
         <v>-0.1257</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.015</v>
+        <v>-0.0182</v>
       </c>
       <c r="Q2" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0334</v>
+        <v>0.032</v>
       </c>
       <c r="S2" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T2" t="n">
         <v>-0.0919</v>
@@ -3631,13 +5067,13 @@
         <v>-0.1528</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0155</v>
+        <v>0.0174</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3643</v>
+        <v>0.4607</v>
       </c>
       <c r="AH2" t="n">
-        <v>42.13</v>
+        <v>40.87</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -3646,13 +5082,13 @@
         <v>-0.0111</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.048309</v>
+        <v>0.015235</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.906627</v>
+        <v>0.87697</v>
       </c>
       <c r="AM2" t="n">
-        <v>-9.34</v>
+        <v>-12.3</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -3682,10 +5118,10 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.043208</v>
+        <v>0.048542</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.1181</v>
+        <v>0.3138</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -3695,7 +5131,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -3837,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.4482</v>
       </c>
       <c r="CQ2" t="n">
         <v>0</v>
@@ -3866,7 +5302,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3899,7 +5335,7 @@
         <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0931</v>
+        <v>0.0929</v>
       </c>
       <c r="L3" t="n">
         <v>0.6977</v>
@@ -3914,16 +5350,16 @@
         <v>0.6267</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0377</v>
+        <v>-0.0453</v>
       </c>
       <c r="Q3" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0365</v>
+        <v>0.0333</v>
       </c>
       <c r="S3" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T3" t="n">
         <v>0.3211</v>
@@ -3964,28 +5400,28 @@
         <v>0.2186</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0192</v>
+        <v>0.0184</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0482</v>
+        <v>0.0276</v>
       </c>
       <c r="AH3" t="n">
-        <v>42.47</v>
+        <v>42.35</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0299</v>
+        <v>0.0298</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.062183</v>
+        <v>0.064446</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.273786</v>
+        <v>1.299552</v>
       </c>
       <c r="AM3" t="n">
-        <v>27.38</v>
+        <v>29.96</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -4015,10 +5451,10 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.053629</v>
+        <v>0.051306</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.1595</v>
+        <v>1.2561</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -4166,7 +5602,7 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.5693</v>
+        <v>0.583</v>
       </c>
       <c r="CQ3" t="n">
         <v>0</v>
@@ -4195,7 +5631,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4221,7 +5657,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -4243,13 +5679,13 @@
         <v>0.0438</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1885</v>
+        <v>0.1958</v>
       </c>
       <c r="Q4" t="n">
         <v>443</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2976</v>
+        <v>0.3031</v>
       </c>
       <c r="S4" t="n">
         <v>229</v>
@@ -4262,20 +5698,20 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>0.4372</v>
+        <v>0.3843</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.3662</v>
+        <v>1.5058</v>
       </c>
       <c r="AA4" t="n">
         <v>0.1762</v>
@@ -4293,13 +5729,13 @@
         <v>0.3843</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0146</v>
+        <v>0.0162</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4978</v>
+        <v>0.6142</v>
       </c>
       <c r="AH4" t="n">
-        <v>41.83</v>
+        <v>40.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -4308,13 +5744,13 @@
         <v>0.0011</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.006</v>
+        <v>-0.027616</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.983335</v>
+        <v>0.990783</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1.67</v>
+        <v>-0.92</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -4344,10 +5780,10 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.040865</v>
+        <v>0.045194</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1468</v>
+        <v>0.611</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -4357,7 +5793,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -4499,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.4336</v>
+        <v>0.4567</v>
       </c>
       <c r="CQ4" t="n">
         <v>0</v>
@@ -4528,7 +5964,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4537,7 +5973,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4546,15 +5982,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4626,28 +6066,28 @@
         <v>0.2427</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0159</v>
+        <v>0.0155</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5191</v>
+        <v>0.4989</v>
       </c>
       <c r="AH5" t="n">
-        <v>75.39</v>
+        <v>74.97</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>77.67</v>
       </c>
       <c r="AJ5" t="n">
         <v>0.2289</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.033101</v>
+        <v>0.034882</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.057983</v>
+        <v>1.107236</v>
       </c>
       <c r="AM5" t="n">
-        <v>5.8</v>
+        <v>10.72</v>
       </c>
       <c r="AN5" t="n">
         <v>1</v>
@@ -4656,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -4674,13 +6114,13 @@
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.044373</v>
+        <v>0.043256</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.746</v>
+        <v>0.8064</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -4690,12 +6130,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BC5" t="n">
@@ -4832,27 +6272,71 @@
         <v>1</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.4719</v>
+        <v>0.482</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
+        <v>0.482</v>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>Call delta~50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>naked_30: esp=+0.634 | spread_35_20: esp=+0.132 | spread_45_25: esp=+0.142 | spread_45_15: esp=+0.243</t>
+        </is>
+      </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Ticker neutro — sem sinal operacional</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="inlineStr"/>
-      <c r="DC5" t="inlineStr"/>
+          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.746 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>80% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>40% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4861,7 +6345,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4898,28 +6382,28 @@
         <v>193</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4168</v>
+        <v>0.4159</v>
       </c>
       <c r="L6" t="n">
         <v>0.6839</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3547</v>
+        <v>0.3529</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9006</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1115</v>
+        <v>0.1111</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1049</v>
+        <v>0.1047</v>
       </c>
       <c r="Q6" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1306</v>
+        <v>0.1302</v>
       </c>
       <c r="S6" t="n">
         <v>405</v>
@@ -4928,7 +6412,7 @@
         <v>0.2293</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0482</v>
+        <v>0.0481</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -4942,16 +6426,16 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>0.3108</v>
+        <v>0.3107</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9711</v>
+        <v>0.9709</v>
       </c>
       <c r="AA6" t="n">
         <v>0.2283</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3108</v>
+        <v>0.3107</v>
       </c>
       <c r="AC6" t="n">
         <v>0.06370000000000001</v>
@@ -4960,31 +6444,31 @@
         <v>0.0877</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1372</v>
+        <v>0.1371</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0135</v>
+        <v>0.014</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2985</v>
+        <v>0.3393</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.7</v>
+        <v>17.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>17.15</v>
+        <v>16.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0956</v>
+        <v>0.0954</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.039926</v>
+        <v>-0.07148599999999999</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.095515</v>
+        <v>1.144711</v>
       </c>
       <c r="AM6" t="n">
-        <v>9.550000000000001</v>
+        <v>14.47</v>
       </c>
       <c r="AN6" t="n">
         <v>1</v>
@@ -5014,10 +6498,10 @@
         <v>-1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.037621</v>
+        <v>0.039153</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.0613</v>
+        <v>1.8258</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -5169,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.5405</v>
+        <v>0.6088</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.5405</v>
+        <v>0.6088</v>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
@@ -5242,7 +6726,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5344,13 +6828,13 @@
         <v>-0.0297</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02</v>
+        <v>0.0212</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.3206</v>
+        <v>0.3697</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.36</v>
+        <v>14.95</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -5359,13 +6843,13 @@
         <v>0.0017</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.012798</v>
+        <v>0.002184</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.023933</v>
+        <v>1.023418</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -5395,10 +6879,10 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.055826</v>
+        <v>0.059282</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2292</v>
+        <v>0.0368</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -5550,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.4213</v>
+        <v>0.3922</v>
       </c>
       <c r="CQ7" t="n">
         <v>0</v>
@@ -5579,7 +7063,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5588,7 +7072,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5597,15 +7081,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -5618,7 +7106,7 @@
         <v>0.4333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3046</v>
+        <v>0.3026</v>
       </c>
       <c r="N8" t="n">
         <v>0.8581</v>
@@ -5642,7 +7130,7 @@
         <v>0.1379</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0479</v>
+        <v>0.0478</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -5677,28 +7165,28 @@
         <v>0.0302</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0339</v>
+        <v>0.0348</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.3701</v>
+        <v>0.4071</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.57</v>
+        <v>4.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.0447</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.066167</v>
+        <v>-0.083866</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.088536</v>
+        <v>1.073351</v>
       </c>
       <c r="AM8" t="n">
-        <v>8.85</v>
+        <v>7.34</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
@@ -5725,13 +7213,13 @@
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.094628</v>
+        <v>0.096987</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.6992</v>
+        <v>0.8647</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -5741,7 +7229,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -5883,27 +7371,71 @@
         <v>1</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.4931</v>
+        <v>0.5022</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR8" t="inlineStr"/>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="inlineStr"/>
-      <c r="CW8" t="inlineStr"/>
+        <v>0.5022</v>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>OTM extremo sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>naked_30: esp=+0.137 | spread_35_20: esp=+0.015 | spread_45_25: esp=+0.002 | spread_45_15: esp=+0.030</t>
+        </is>
+      </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>Ticker neutro — sem sinal operacional</t>
-        </is>
-      </c>
-      <c r="CY8" t="inlineStr"/>
-      <c r="CZ8" t="inlineStr"/>
-      <c r="DA8" t="inlineStr"/>
-      <c r="DB8" t="inlineStr"/>
-      <c r="DC8" t="inlineStr"/>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.148 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>80% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>40% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5912,7 +7444,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5938,7 +7470,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -5960,13 +7492,13 @@
         <v>0.3423</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02</v>
+        <v>0.0086</v>
       </c>
       <c r="Q9" t="n">
         <v>443</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0435</v>
+        <v>0.0305</v>
       </c>
       <c r="S9" t="n">
         <v>364</v>
@@ -6010,13 +7542,13 @@
         <v>-0.0117</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0178</v>
+        <v>0.0202</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.3943</v>
+        <v>0.5065</v>
       </c>
       <c r="AH9" t="n">
-        <v>47.31</v>
+        <v>45.69</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -6025,13 +7557,13 @@
         <v>0.0272</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.031972</v>
+        <v>0.013359</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.937214</v>
+        <v>0.95238</v>
       </c>
       <c r="AM9" t="n">
-        <v>-6.28</v>
+        <v>-4.76</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -6061,10 +7593,10 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.049623</v>
+        <v>0.056366</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.6443</v>
+        <v>0.237</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -6074,7 +7606,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -6216,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.5006</v>
+        <v>0.4375</v>
       </c>
       <c r="CQ9" t="n">
         <v>0</v>
@@ -6245,7 +7777,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6259,7 +7791,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -6343,13 +7875,13 @@
         <v>0.284</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0146</v>
+        <v>0.0157</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.46</v>
+        <v>0.5386</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.51</v>
+        <v>13.21</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -6358,13 +7890,13 @@
         <v>0.0076</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.003659</v>
+        <v>-0.013946</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.000891</v>
+        <v>0.976691</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.09</v>
+        <v>-2.33</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -6394,10 +7926,10 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.040672</v>
+        <v>0.043936</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.09</v>
+        <v>0.3174</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -6412,7 +7944,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
       <c r="BC10" t="n">
@@ -6549,7 +8081,7 @@
         <v>1</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.4129</v>
+        <v>0.42</v>
       </c>
       <c r="CQ10" t="n">
         <v>0</v>
@@ -6578,7 +8110,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6676,13 +8208,13 @@
         <v>0.1656</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0171</v>
+        <v>0.0187</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.4363</v>
+        <v>0.5366</v>
       </c>
       <c r="AH11" t="n">
-        <v>25.65</v>
+        <v>25.05</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -6691,13 +8223,13 @@
         <v>0.0645</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.109722</v>
+        <v>0.083079</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.9649219999999999</v>
+        <v>0.942769</v>
       </c>
       <c r="AM11" t="n">
-        <v>-3.51</v>
+        <v>-5.72</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -6709,7 +8241,7 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>1.049377</v>
@@ -6727,10 +8259,10 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.047789</v>
+        <v>0.05214</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.296</v>
+        <v>1.5934</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -6882,7 +8414,7 @@
         <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.5648</v>
+        <v>0.5041</v>
       </c>
       <c r="CQ11" t="n">
         <v>0</v>
@@ -6911,7 +8443,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -7013,13 +8545,13 @@
         <v>-0.0557</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0314</v>
+        <v>0.0296</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.5391</v>
+        <v>0.4725</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.19</v>
+        <v>7.15</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -7028,13 +8560,13 @@
         <v>-0.0071</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.12274</v>
+        <v>-0.115741</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.012538</v>
+        <v>1.060653</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.25</v>
+        <v>6.07</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -7064,10 +8596,10 @@
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.087557</v>
+        <v>0.08269</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.4018</v>
+        <v>1.3997</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -7219,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.5322</v>
+        <v>0.5453</v>
       </c>
       <c r="CQ12" t="n">
         <v>0</v>
@@ -7248,7 +8780,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -7274,7 +8806,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -7302,7 +8834,7 @@
         <v>443</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1291</v>
+        <v>-0.1281</v>
       </c>
       <c r="S13" t="n">
         <v>337</v>
@@ -7320,7 +8852,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -7350,13 +8882,13 @@
         <v>-0.0089</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0198</v>
+        <v>0.0304</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.2192</v>
+        <v>0.7392</v>
       </c>
       <c r="AH13" t="n">
-        <v>13.48</v>
+        <v>12.39</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -7365,19 +8897,19 @@
         <v>-0.0038</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.008977000000000001</v>
+        <v>-0.053109</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.066399</v>
+        <v>0.938655</v>
       </c>
       <c r="AM13" t="n">
-        <v>6.64</v>
+        <v>-6.13</v>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -7395,16 +8927,16 @@
         <v>0.9088889999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.055392</v>
+        <v>0.084825</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1621</v>
+        <v>0.6261</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,12 +8946,12 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
       <c r="BC13" t="n">
@@ -7552,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.5003</v>
+        <v>0.4427</v>
       </c>
       <c r="CQ13" t="n">
         <v>0</v>
@@ -7581,7 +9113,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7607,7 +9139,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -7629,13 +9161,13 @@
         <v>0.0344</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0505</v>
+        <v>0.046</v>
       </c>
       <c r="Q14" t="n">
         <v>443</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0859</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>346</v>
@@ -7679,13 +9211,13 @@
         <v>0.0323</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0136</v>
+        <v>0.0143</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.5271</v>
+        <v>0.5788</v>
       </c>
       <c r="AH14" t="n">
-        <v>40.96</v>
+        <v>38.38</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -7694,13 +9226,13 @@
         <v>0.008200000000000001</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.023785</v>
+        <v>0.012802</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.960512</v>
+        <v>0.949518</v>
       </c>
       <c r="AM14" t="n">
-        <v>-3.95</v>
+        <v>-5.05</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -7730,10 +9262,10 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.037983</v>
+        <v>0.0399</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.6262</v>
+        <v>0.3209</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7743,7 +9275,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -7881,7 +9413,7 @@
         <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.3226</v>
+        <v>0.2818</v>
       </c>
       <c r="CQ14" t="n">
         <v>0</v>
@@ -7910,7 +9442,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -8008,13 +9540,13 @@
         <v>0.3761</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0377</v>
+        <v>0.0408</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2181</v>
+        <v>0.2464</v>
       </c>
       <c r="AH15" t="n">
-        <v>11.13</v>
+        <v>10.77</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -8023,13 +9555,13 @@
         <v>0.3766</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.009139</v>
+        <v>-0.037512</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.90011</v>
+        <v>0.887463</v>
       </c>
       <c r="AM15" t="n">
-        <v>-9.99</v>
+        <v>-11.25</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -8059,10 +9591,10 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.105239</v>
+        <v>0.113908</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0868</v>
+        <v>0.3293</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -8214,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.4456</v>
+        <v>0.4642</v>
       </c>
       <c r="CQ15" t="n">
         <v>0</v>
@@ -8243,7 +9775,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -8257,7 +9789,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -8345,13 +9877,13 @@
         <v>-0.1049</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0251</v>
+        <v>0.0255</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1978</v>
+        <v>0.2134</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.57</v>
+        <v>4.46</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -8360,13 +9892,13 @@
         <v>-0.0153</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.010254</v>
+        <v>-0.012393</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.021692</v>
+        <v>1.008644</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.17</v>
+        <v>0.86</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -8396,10 +9928,10 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.070009</v>
+        <v>0.0712</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1465</v>
+        <v>0.1741</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -8551,7 +10083,7 @@
         <v>1</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.4767</v>
+        <v>0.4763</v>
       </c>
       <c r="CQ16" t="n">
         <v>0</v>
@@ -8580,7 +10112,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -8594,7 +10126,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -8682,13 +10214,13 @@
         <v>-0.0337</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0113</v>
+        <v>0.0115</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0418</v>
+        <v>0.0456</v>
       </c>
       <c r="AH17" t="n">
-        <v>15.66</v>
+        <v>15.48</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -8697,13 +10229,13 @@
         <v>0.0066</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.007826</v>
+        <v>-0.001979</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.188564</v>
+        <v>1.187961</v>
       </c>
       <c r="AM17" t="n">
-        <v>18.86</v>
+        <v>18.8</v>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
@@ -8733,10 +10265,10 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.031591</v>
+        <v>0.031991</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.2477</v>
+        <v>0.0619</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -8888,7 +10420,7 @@
         <v>0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.4657</v>
+        <v>0.4463</v>
       </c>
       <c r="CQ17" t="n">
         <v>0</v>
@@ -8917,7 +10449,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -9003,13 +10535,13 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.0427</v>
+        <v>0.0448</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.6957</v>
+        <v>0.7514</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.74</v>
+        <v>4.57</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -9018,13 +10550,13 @@
         <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-0.050131</v>
+        <v>-0.072612</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.825559</v>
+        <v>0.860874</v>
       </c>
       <c r="AM18" t="n">
-        <v>-17.44</v>
+        <v>-13.91</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -9048,16 +10580,16 @@
         <v>0.933359</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.119075</v>
+        <v>0.12506</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.421</v>
+        <v>0.5806</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -9205,7 +10737,7 @@
         <v>1</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.406</v>
+        <v>0.4108</v>
       </c>
       <c r="CQ18" t="n">
         <v>0</v>
@@ -9234,7 +10766,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -9282,13 +10814,13 @@
         <v>0.1862</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.0157</v>
+        <v>-0.0107</v>
       </c>
       <c r="Q19" t="n">
         <v>443</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2709</v>
+        <v>0.2725</v>
       </c>
       <c r="S19" t="n">
         <v>231</v>
@@ -9332,13 +10864,13 @@
         <v>0.2147</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0125</v>
+        <v>0.0123</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.4733</v>
+        <v>0.4593</v>
       </c>
       <c r="AH19" t="n">
-        <v>39.54</v>
+        <v>39.25</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -9347,13 +10879,13 @@
         <v>0.1381</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.004092</v>
+        <v>-0.009245</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.804005</v>
+        <v>0.812528</v>
       </c>
       <c r="AM19" t="n">
-        <v>-19.6</v>
+        <v>-18.75</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -9383,10 +10915,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.034816</v>
+        <v>0.034254</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.1175</v>
+        <v>0.2699</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -9534,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.3799</v>
+        <v>0.3979</v>
       </c>
       <c r="CQ19" t="n">
         <v>0</v>
@@ -9563,7 +11095,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -9589,7 +11121,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -9661,13 +11193,13 @@
         <v>0.1343</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0205</v>
+        <v>0.0204</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
       <c r="AH20" t="n">
-        <v>21.83</v>
+        <v>21.67</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -9676,13 +11208,13 @@
         <v>0.0216</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.030571</v>
+        <v>0.03435</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.996385</v>
+        <v>0.997312</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0.36</v>
+        <v>-0.27</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -9712,10 +11244,10 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.057097</v>
+        <v>0.05697</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.5354</v>
+        <v>0.603</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -9725,7 +11257,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -9867,7 +11399,7 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.4656</v>
+        <v>0.4725</v>
       </c>
       <c r="CQ20" t="n">
         <v>0</v>
@@ -9896,7 +11428,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -10001,10 +11533,10 @@
         <v>0.0249</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.241</v>
+        <v>0.2412</v>
       </c>
       <c r="AH21" t="n">
-        <v>20.12</v>
+        <v>20.22</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -10013,13 +11545,13 @@
         <v>0.0113</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.08225</v>
+        <v>0.08019900000000001</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.918342</v>
+        <v>0.903408</v>
       </c>
       <c r="AM21" t="n">
-        <v>-8.17</v>
+        <v>-9.66</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -10049,10 +11581,10 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.069463</v>
+        <v>0.069478</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.1841</v>
+        <v>1.1543</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -10204,7 +11736,7 @@
         <v>1</v>
       </c>
       <c r="CP21" t="n">
-        <v>0.5441</v>
+        <v>0.5411</v>
       </c>
       <c r="CQ21" t="n">
         <v>0</v>
@@ -10233,7 +11765,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -10278,7 +11810,7 @@
         <v>1.0452</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6563</v>
+        <v>0.6562</v>
       </c>
       <c r="P22" t="n">
         <v>0.2493</v>
@@ -10331,13 +11863,13 @@
         <v>0.1485</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.0246</v>
+        <v>0.0247</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.3943</v>
+        <v>0.3952</v>
       </c>
       <c r="AH22" t="n">
-        <v>10.67</v>
+        <v>10.79</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -10346,13 +11878,13 @@
         <v>0.0518</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.003236</v>
+        <v>0.004398</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.172143</v>
+        <v>1.17299</v>
       </c>
       <c r="AM22" t="n">
-        <v>17.21</v>
+        <v>17.3</v>
       </c>
       <c r="AN22" t="n">
         <v>1</v>
@@ -10382,10 +11914,10 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.068755</v>
+        <v>0.06882199999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.0471</v>
+        <v>0.0639</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -10533,7 +12065,7 @@
         <v>0</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.3642</v>
+        <v>0.3657</v>
       </c>
       <c r="CQ22" t="n">
         <v>0</v>
@@ -10562,7 +12094,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -10588,7 +12120,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -10664,13 +12196,13 @@
         <v>-0.0616</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.021</v>
+        <v>0.0212</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.5113</v>
+        <v>0.5198</v>
       </c>
       <c r="AH23" t="n">
-        <v>27.39</v>
+        <v>26.89</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -10679,13 +12211,13 @@
         <v>-0.0189</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.041062</v>
+        <v>-0.055409</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.018737</v>
+        <v>1.023067</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.87</v>
+        <v>2.31</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -10715,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.058633</v>
+        <v>0.059189</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.7003</v>
+        <v>0.9361</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -10728,7 +12260,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -10870,7 +12402,7 @@
         <v>1</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.4754</v>
+        <v>0.4973</v>
       </c>
       <c r="CQ23" t="n">
         <v>0</v>
@@ -10899,7 +12431,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -10997,13 +12529,13 @@
         <v>0.131</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0176</v>
+        <v>0.0179</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.4584</v>
+        <v>0.4856</v>
       </c>
       <c r="AH24" t="n">
-        <v>11.2</v>
+        <v>11.01</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -11012,13 +12544,13 @@
         <v>0.0473</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.092775</v>
+        <v>0.082331</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.05328</v>
+        <v>1.071506</v>
       </c>
       <c r="AM24" t="n">
-        <v>5.33</v>
+        <v>7.15</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
@@ -11048,10 +12580,10 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.048981</v>
+        <v>0.050069</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.8941</v>
+        <v>1.6444</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -11203,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.5573</v>
+        <v>0.5269</v>
       </c>
       <c r="CQ24" t="n">
         <v>0</v>
@@ -11232,7 +12764,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -11286,7 +12818,7 @@
         <v>443</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1206</v>
+        <v>0.1054</v>
       </c>
       <c r="S25" t="n">
         <v>353</v>
@@ -11330,13 +12862,13 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0169</v>
+        <v>0.0167</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.4979</v>
+        <v>0.4808</v>
       </c>
       <c r="AH25" t="n">
-        <v>29.91</v>
+        <v>29.73</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -11345,13 +12877,13 @@
         <v>0.006</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.002893</v>
+        <v>-0.005545</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.956992</v>
+        <v>0.957136</v>
       </c>
       <c r="AM25" t="n">
-        <v>-4.3</v>
+        <v>-4.29</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -11381,10 +12913,10 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.047301</v>
+        <v>0.046565</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.0612</v>
+        <v>0.1191</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -11536,7 +13068,7 @@
         <v>1</v>
       </c>
       <c r="CP25" t="n">
-        <v>0.4031</v>
+        <v>0.4123</v>
       </c>
       <c r="CQ25" t="n">
         <v>0</v>
@@ -11565,7 +13097,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -11604,7 +13136,7 @@
         <v>0.6351</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3919</v>
+        <v>0.3893</v>
       </c>
       <c r="N26" t="n">
         <v>1.5772</v>
@@ -11628,7 +13160,7 @@
         <v>0.515</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0853</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -11663,13 +13195,13 @@
         <v>0.1396</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0158</v>
+        <v>0.0149</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.499</v>
+        <v>0.4566</v>
       </c>
       <c r="AH26" t="n">
-        <v>21.66</v>
+        <v>21.35</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -11678,19 +13210,19 @@
         <v>0.1646</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.031165</v>
+        <v>0.025235</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.994227</v>
+        <v>1.058818</v>
       </c>
       <c r="AM26" t="n">
-        <v>-0.58</v>
+        <v>5.88</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26" t="n">
         <v>0</v>
@@ -11714,10 +13246,10 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.043984</v>
+        <v>0.04163</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.7086</v>
+        <v>0.6062</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -11869,7 +13401,7 @@
         <v>0</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.4393</v>
+        <v>0.4376</v>
       </c>
       <c r="CQ26" t="n">
         <v>0</v>
@@ -11898,7 +13430,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -12000,13 +13532,13 @@
         <v>-0.2219</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0333</v>
+        <v>0.0335</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.165</v>
+        <v>0.167</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.05</v>
+        <v>5.94</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -12015,13 +13547,13 @@
         <v>-0.0089</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.012996</v>
+        <v>-0.014846</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.183461</v>
+        <v>1.117484</v>
       </c>
       <c r="AM27" t="n">
-        <v>18.35</v>
+        <v>11.75</v>
       </c>
       <c r="AN27" t="n">
         <v>1</v>
@@ -12051,10 +13583,10 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.09299200000000001</v>
+        <v>0.093376</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.1398</v>
+        <v>0.159</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -12202,7 +13734,7 @@
         <v>0</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.4516</v>
+        <v>0.4532</v>
       </c>
       <c r="CQ27" t="n">
         <v>0</v>
@@ -12231,7 +13763,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -12333,13 +13865,13 @@
         <v>0.0148</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0249</v>
+        <v>0.0241</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.5547</v>
+        <v>0.5223</v>
       </c>
       <c r="AH28" t="n">
-        <v>11.75</v>
+        <v>11.58</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -12348,13 +13880,13 @@
         <v>0.0152</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.008059</v>
+        <v>-0.013989</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.046879</v>
+        <v>1.069021</v>
       </c>
       <c r="AM28" t="n">
-        <v>4.69</v>
+        <v>6.9</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
@@ -12384,10 +13916,10 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.06955799999999999</v>
+        <v>0.067194</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.1159</v>
+        <v>0.2082</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -12535,7 +14067,7 @@
         <v>0</v>
       </c>
       <c r="CP28" t="n">
-        <v>0.349</v>
+        <v>0.3647</v>
       </c>
       <c r="CQ28" t="n">
         <v>0</v>
@@ -12564,7 +14096,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -12578,7 +14110,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -12669,10 +14201,10 @@
         <v>0.0208</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2225</v>
+        <v>0.222</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -12681,13 +14213,13 @@
         <v>-0.0028</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.011845</v>
+        <v>-0.000155</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.081126</v>
+        <v>1.076263</v>
       </c>
       <c r="AM29" t="n">
-        <v>8.109999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="AN29" t="n">
         <v>0</v>
@@ -12717,10 +14249,10 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.058136</v>
+        <v>0.058088</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.2037</v>
+        <v>0.0027</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -12868,7 +14400,7 @@
         <v>0</v>
       </c>
       <c r="CP29" t="n">
-        <v>0.4616</v>
+        <v>0.4416</v>
       </c>
       <c r="CQ29" t="n">
         <v>0</v>
@@ -12897,7 +14429,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -12939,7 +14471,7 @@
         <v>0.3453</v>
       </c>
       <c r="N30" t="n">
-        <v>0.7458</v>
+        <v>0.7528</v>
       </c>
       <c r="O30" t="n">
         <v>0.0333</v>
@@ -12957,10 +14489,10 @@
         <v>328</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1714</v>
+        <v>0.174</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0528</v>
+        <v>0.0534</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -12984,10 +14516,10 @@
         <v>0.4563</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.1704</v>
+        <v>0.173</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.2487</v>
+        <v>0.2513</v>
       </c>
       <c r="AC30" t="n">
         <v>0.0556</v>
@@ -12999,28 +14531,28 @@
         <v>0.1164</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0317</v>
+        <v>0.0304</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.785</v>
+        <v>0.7408</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.0474</v>
+        <v>0.0481</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.106796</v>
+        <v>-0.111033</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.897848</v>
+        <v>0.909181</v>
       </c>
       <c r="AM30" t="n">
-        <v>-10.22</v>
+        <v>-9.08</v>
       </c>
       <c r="AN30" t="n">
         <v>0</v>
@@ -13050,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.088403</v>
+        <v>0.084926</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.2081</v>
+        <v>1.3074</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -13205,7 +14737,7 @@
         <v>1</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.4739</v>
+        <v>0.4927</v>
       </c>
       <c r="CQ30" t="n">
         <v>0</v>
@@ -13234,7 +14766,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -13282,13 +14814,13 @@
         <v>-0.1435</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0521</v>
+        <v>0.0539</v>
       </c>
       <c r="Q31" t="n">
         <v>443</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0327</v>
+        <v>0.0415</v>
       </c>
       <c r="S31" t="n">
         <v>287</v>
@@ -13336,13 +14868,13 @@
         <v>0.0499</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0157</v>
+        <v>0.0163</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.3493</v>
+        <v>0.3833</v>
       </c>
       <c r="AH31" t="n">
-        <v>14.9</v>
+        <v>14.67</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -13351,13 +14883,13 @@
         <v>0.0441</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.001531</v>
+        <v>-0.010152</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.111426</v>
+        <v>1.110031</v>
       </c>
       <c r="AM31" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="AN31" t="n">
         <v>1</v>
@@ -13387,10 +14919,10 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.043867</v>
+        <v>0.045529</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.0349</v>
+        <v>0.223</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -13538,7 +15070,7 @@
         <v>0</v>
       </c>
       <c r="CP31" t="n">
-        <v>0.3624</v>
+        <v>0.3744</v>
       </c>
       <c r="CQ31" t="n">
         <v>0</v>
@@ -13567,7 +15099,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -13606,10 +15138,10 @@
         <v>0.6667</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0794</v>
+        <v>0.0806</v>
       </c>
       <c r="N32" t="n">
-        <v>0.4674</v>
+        <v>0.2762</v>
       </c>
       <c r="O32" t="n">
         <v>-0.18</v>
@@ -13627,10 +15159,10 @@
         <v>306</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.1036</v>
+        <v>-0.1251</v>
       </c>
       <c r="U32" t="n">
-        <v>0.031</v>
+        <v>0.0188</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -13654,43 +15186,43 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.1046</v>
+        <v>-0.1261</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.137</v>
+        <v>-0.1586</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.0597</v>
+        <v>-0.06</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0684</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.0147</v>
+        <v>0.0142</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.4871</v>
+        <v>0.4546</v>
       </c>
       <c r="AH32" t="n">
-        <v>18.02</v>
+        <v>18.01</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-0.0101</v>
+        <v>-0.0122</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.012954</v>
+        <v>0.00458</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.113749</v>
+        <v>1.112795</v>
       </c>
       <c r="AM32" t="n">
-        <v>11.37</v>
+        <v>11.28</v>
       </c>
       <c r="AN32" t="n">
         <v>0</v>
@@ -13720,10 +15252,10 @@
         <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.040948</v>
+        <v>0.039696</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.3163</v>
+        <v>0.1154</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -13871,7 +15403,7 @@
         <v>0</v>
       </c>
       <c r="CP32" t="n">
-        <v>0.3861</v>
+        <v>0.3725</v>
       </c>
       <c r="CQ32" t="n">
         <v>0</v>
@@ -13900,7 +15432,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -13914,7 +15446,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -13998,13 +15530,13 @@
         <v>0.0975</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.0155</v>
+        <v>0.0152</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.3329</v>
+        <v>0.3172</v>
       </c>
       <c r="AH33" t="n">
-        <v>27</v>
+        <v>26.94</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -14013,13 +15545,13 @@
         <v>0.0105</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.001419</v>
+        <v>-0.00226</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.860057</v>
+        <v>0.866009</v>
       </c>
       <c r="AM33" t="n">
-        <v>-13.99</v>
+        <v>-13.4</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -14049,10 +15581,10 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.043288</v>
+        <v>0.042374</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.0328</v>
+        <v>0.0533</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -14204,7 +15736,7 @@
         <v>1</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.4006</v>
+        <v>0.4058</v>
       </c>
       <c r="CQ33" t="n">
         <v>0</v>
@@ -14233,7 +15765,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -14247,7 +15779,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -14281,13 +15813,13 @@
         <v>2.3122</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.1225</v>
+        <v>-0.1276</v>
       </c>
       <c r="Q34" t="n">
         <v>443</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.135</v>
+        <v>-0.1638</v>
       </c>
       <c r="S34" t="n">
         <v>301</v>
@@ -14325,19 +15857,19 @@
         <v>0.0438</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.0104</v>
+        <v>0.0105</v>
       </c>
       <c r="AE34" t="n">
         <v>0.07099999999999999</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0173</v>
+        <v>0.0223</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.2947</v>
+        <v>0.5458</v>
       </c>
       <c r="AH34" t="n">
-        <v>32.75</v>
+        <v>31.28</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -14346,13 +15878,13 @@
         <v>0.0374</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.021093</v>
+        <v>-0.008978</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.8718360000000001</v>
+        <v>0.695875</v>
       </c>
       <c r="AM34" t="n">
-        <v>-12.82</v>
+        <v>-30.41</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -14382,10 +15914,10 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.048275</v>
+        <v>0.062278</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.4369</v>
+        <v>0.1442</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -14533,7 +16065,7 @@
         <v>0</v>
       </c>
       <c r="CP34" t="n">
-        <v>0.4474</v>
+        <v>0.3679</v>
       </c>
       <c r="CQ34" t="n">
         <v>0</v>
@@ -14562,7 +16094,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -14664,13 +16196,13 @@
         <v>-0.1592</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.0191</v>
+        <v>0.0187</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.2723</v>
+        <v>0.2523</v>
       </c>
       <c r="AH35" t="n">
-        <v>21.33</v>
+        <v>21.6</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -14679,13 +16211,13 @@
         <v>-0.0078</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.023352</v>
+        <v>0.031145</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.9491849999999999</v>
+        <v>0.944399</v>
       </c>
       <c r="AM35" t="n">
-        <v>-5.08</v>
+        <v>-5.56</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -14715,10 +16247,10 @@
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.053384</v>
+        <v>0.052145</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.4374</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -14866,7 +16398,7 @@
         <v>0</v>
       </c>
       <c r="CP35" t="n">
-        <v>0.456</v>
+        <v>0.476</v>
       </c>
       <c r="CQ35" t="n">
         <v>0</v>
@@ -14895,7 +16427,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -14931,7 +16463,7 @@
         <v>0.108</v>
       </c>
       <c r="L36" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="M36" t="n">
         <v>0.36</v>
@@ -14993,13 +16525,13 @@
         <v>0.063</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.0201</v>
+        <v>0.0196</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.5887</v>
+        <v>0.5635</v>
       </c>
       <c r="AH36" t="n">
-        <v>27.88</v>
+        <v>27.79</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -15008,13 +16540,13 @@
         <v>0.0102</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.028088</v>
+        <v>-0.029859</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.84424</v>
+        <v>0.840808</v>
       </c>
       <c r="AM36" t="n">
-        <v>-15.58</v>
+        <v>-15.92</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -15044,10 +16576,10 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.056122</v>
+        <v>0.054663</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5462</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -15199,7 +16731,7 @@
         <v>0</v>
       </c>
       <c r="CP36" t="n">
-        <v>0.383</v>
+        <v>0.3926</v>
       </c>
       <c r="CQ36" t="n">
         <v>0</v>
@@ -15228,7 +16760,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -15326,13 +16858,13 @@
         <v>0.1984</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.0189</v>
+        <v>0.02</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.2531</v>
+        <v>0.2841</v>
       </c>
       <c r="AH37" t="n">
-        <v>63.35</v>
+        <v>61.94</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -15341,13 +16873,13 @@
         <v>0.0159</v>
       </c>
       <c r="AK37" t="n">
-        <v>-0.001014</v>
+        <v>-0.012201</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.766845</v>
+        <v>0.756908</v>
       </c>
       <c r="AM37" t="n">
-        <v>-23.32</v>
+        <v>-24.31</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -15377,10 +16909,10 @@
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.052632</v>
+        <v>0.055836</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.0193</v>
+        <v>0.2185</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -15528,7 +17060,7 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>0.4289</v>
+        <v>0.4426</v>
       </c>
       <c r="CQ37" t="n">
         <v>0</v>
@@ -15557,7 +17089,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -15571,7 +17103,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -15605,13 +17137,13 @@
         <v>-0.18</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.1693</v>
+        <v>-0.1683</v>
       </c>
       <c r="Q38" t="n">
         <v>443</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.0643</v>
+        <v>-0.0735</v>
       </c>
       <c r="S38" t="n">
         <v>316</v>
@@ -15655,13 +17187,13 @@
         <v>0.0197</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0223</v>
+        <v>0.0238</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.1235</v>
       </c>
       <c r="AH38" t="n">
-        <v>8.24</v>
+        <v>7.96</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -15670,13 +17202,13 @@
         <v>0.0086</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.015062</v>
+        <v>-0.011262</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.145373</v>
+        <v>1.122118</v>
       </c>
       <c r="AM38" t="n">
-        <v>14.54</v>
+        <v>12.21</v>
       </c>
       <c r="AN38" t="n">
         <v>1</v>
@@ -15706,10 +17238,10 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.0621</v>
+        <v>0.066465</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.2425</v>
+        <v>0.1694</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -15861,7 +17393,7 @@
         <v>1</v>
       </c>
       <c r="CP38" t="n">
-        <v>0.504</v>
+        <v>0.4859</v>
       </c>
       <c r="CQ38" t="n">
         <v>0</v>
@@ -15890,7 +17422,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -15988,13 +17520,13 @@
         <v>0.0302</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.0146</v>
+        <v>0.0143</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.4997</v>
+        <v>0.4839</v>
       </c>
       <c r="AH39" t="n">
-        <v>13.21</v>
+        <v>13.22</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -16003,13 +17535,13 @@
         <v>0.0231</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.011096</v>
+        <v>-0.011419</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.130418</v>
+        <v>1.135824</v>
       </c>
       <c r="AM39" t="n">
-        <v>13.04</v>
+        <v>13.58</v>
       </c>
       <c r="AN39" t="n">
         <v>0</v>
@@ -16039,10 +17571,10 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.040723</v>
+        <v>0.039973</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.2725</v>
+        <v>0.2857</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -16194,7 +17726,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>0.4077</v>
+        <v>0.4122</v>
       </c>
       <c r="CQ39" t="n">
         <v>0</v>
@@ -16223,7 +17755,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -16325,13 +17857,13 @@
         <v>-0.0126</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0197</v>
+        <v>0.02</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.6268</v>
+        <v>0.639</v>
       </c>
       <c r="AH40" t="n">
-        <v>26.65</v>
+        <v>26.27</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -16340,13 +17872,13 @@
         <v>0.0107</v>
       </c>
       <c r="AK40" t="n">
-        <v>-0.008</v>
+        <v>-0.010436</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.881378</v>
+        <v>0.887497</v>
       </c>
       <c r="AM40" t="n">
-        <v>-11.86</v>
+        <v>-11.25</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -16376,10 +17908,10 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.055079</v>
+        <v>0.05576</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.1452</v>
+        <v>0.1872</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -16527,7 +18059,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>0.3735</v>
+        <v>0.3753</v>
       </c>
       <c r="CQ40" t="n">
         <v>0</v>
@@ -16556,7 +18088,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -16570,7 +18102,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -16604,13 +18136,13 @@
         <v>1.3175</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.1469</v>
+        <v>-0.1498</v>
       </c>
       <c r="Q41" t="n">
         <v>443</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.158</v>
+        <v>-0.1604</v>
       </c>
       <c r="S41" t="n">
         <v>216</v>
@@ -16661,10 +18193,10 @@
         <v>0.0192</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.5627</v>
+        <v>0.5622</v>
       </c>
       <c r="AH41" t="n">
-        <v>14.64</v>
+        <v>14.49</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -16673,13 +18205,13 @@
         <v>0.0026</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.006336</v>
+        <v>-0.002156</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.865849</v>
+        <v>0.871794</v>
       </c>
       <c r="AM41" t="n">
-        <v>-13.42</v>
+        <v>-12.82</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -16709,10 +18241,10 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.053481</v>
+        <v>0.053459</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.1185</v>
+        <v>0.0403</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -16864,7 +18396,7 @@
         <v>1</v>
       </c>
       <c r="CP41" t="n">
-        <v>0.4193</v>
+        <v>0.4116</v>
       </c>
       <c r="CQ41" t="n">
         <v>0</v>
@@ -16893,7 +18425,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -16919,7 +18451,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -16929,7 +18461,7 @@
         <v>0.1771</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4024</v>
+        <v>0.3902</v>
       </c>
       <c r="M42" t="n">
         <v>0.1829</v>
@@ -16941,13 +18473,13 @@
         <v>-0.0772</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.0585</v>
+        <v>-0.0604</v>
       </c>
       <c r="Q42" t="n">
         <v>443</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.03</v>
+        <v>-0.0393</v>
       </c>
       <c r="S42" t="n">
         <v>332</v>
@@ -16995,13 +18527,13 @@
         <v>-0.07140000000000001</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.0148</v>
+        <v>0.0184</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.3564</v>
+        <v>0.5974</v>
       </c>
       <c r="AH42" t="n">
-        <v>52.65</v>
+        <v>50.42</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -17010,13 +18542,13 @@
         <v>0.0047</v>
       </c>
       <c r="AK42" t="n">
-        <v>-0.005989</v>
+        <v>-0.036041</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.13248</v>
+        <v>1.143755</v>
       </c>
       <c r="AM42" t="n">
-        <v>13.25</v>
+        <v>14.38</v>
       </c>
       <c r="AN42" t="n">
         <v>1</v>
@@ -17046,10 +18578,10 @@
         <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.041208</v>
+        <v>0.051452</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.1453</v>
+        <v>0.7005</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -17059,7 +18591,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -17201,7 +18733,7 @@
         <v>0</v>
       </c>
       <c r="CP42" t="n">
-        <v>0.4389</v>
+        <v>0.4462</v>
       </c>
       <c r="CQ42" t="n">
         <v>0</v>
@@ -17230,7 +18762,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -17276,10 +18808,10 @@
         <v>0.5</v>
       </c>
       <c r="N43" t="n">
-        <v>1.2496</v>
+        <v>1.2606</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7967</v>
+        <v>0.7846</v>
       </c>
       <c r="P43" t="n">
         <v>-0.039</v>
@@ -17294,10 +18826,10 @@
         <v>385</v>
       </c>
       <c r="T43" t="n">
-        <v>0.7107</v>
+        <v>0.7175</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1068</v>
+        <v>0.1075</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -17311,16 +18843,16 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>0.8954</v>
+        <v>0.9023</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.7983</v>
+        <v>2.8196</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.7097</v>
+        <v>0.7165</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.8954</v>
+        <v>0.9023</v>
       </c>
       <c r="AC43" t="n">
         <v>0.1839</v>
@@ -17332,28 +18864,28 @@
         <v>0.3616</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0399</v>
+        <v>0.0455</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.2165</v>
+        <v>0.2919</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.0829</v>
+        <v>0.0837</v>
       </c>
       <c r="AK43" t="n">
-        <v>-0.128275</v>
+        <v>-0.17893</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.122074</v>
+        <v>1.087637</v>
       </c>
       <c r="AM43" t="n">
-        <v>12.21</v>
+        <v>8.76</v>
       </c>
       <c r="AN43" t="n">
         <v>1</v>
@@ -17383,10 +18915,10 @@
         <v>-1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.111329</v>
+        <v>0.126914</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.1522</v>
+        <v>1.4099</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -17534,10 +19066,10 @@
         <v>1</v>
       </c>
       <c r="CP43" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5596</v>
       </c>
       <c r="CQ43" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5596</v>
       </c>
       <c r="CR43" t="inlineStr">
         <is>
@@ -17566,12 +19098,12 @@
       </c>
       <c r="CW43" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.710 | spread_35_20: esp=+0.184 | spread_45_25: esp=+0.229 | spread_45_15: esp=+0.362</t>
+          <t>naked_30: esp=+0.717 | spread_35_20: esp=+0.184 | spread_45_25: esp=+0.229 | spread_45_15: esp=+0.362</t>
         </is>
       </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.895 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.902 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="CY43" t="inlineStr">
@@ -17607,7 +19139,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -17633,7 +19165,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -17674,20 +19206,24 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr"/>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>risco</t>
+        </is>
+      </c>
       <c r="Y44" t="n">
-        <v>0.2298</v>
+        <v>0.118</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.7181</v>
+        <v>0.4625</v>
       </c>
       <c r="AA44" t="n">
         <v>0.1783</v>
@@ -17705,13 +19241,13 @@
         <v>0.118</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0136</v>
+        <v>0.0303</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.2226</v>
+        <v>1</v>
       </c>
       <c r="AH44" t="n">
-        <v>17.27</v>
+        <v>18.95</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -17720,13 +19256,13 @@
         <v>0.0081</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.059797</v>
+        <v>0.06741999999999999</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.10019</v>
+        <v>0.721039</v>
       </c>
       <c r="AM44" t="n">
-        <v>10.02</v>
+        <v>-27.9</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
@@ -17738,7 +19274,7 @@
         <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR44" t="n">
         <v>1.242949</v>
@@ -17750,16 +19286,16 @@
         <v>0.882943</v>
       </c>
       <c r="AU44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.037893</v>
+        <v>0.08459700000000001</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.578</v>
+        <v>0.797</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -17769,12 +19305,12 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
       <c r="BC44" t="n">
@@ -17911,7 +19447,7 @@
         <v>0</v>
       </c>
       <c r="CP44" t="n">
-        <v>0.5994</v>
+        <v>0.3658</v>
       </c>
       <c r="CQ44" t="n">
         <v>0</v>
@@ -17940,7 +19476,7 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -17949,7 +19485,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -17958,15 +19494,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -17979,7 +19519,7 @@
         <v>0.5714</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3721</v>
+        <v>0.3636</v>
       </c>
       <c r="N45" t="n">
         <v>0.4284</v>
@@ -17994,16 +19534,16 @@
         <v>443</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.0016</v>
+        <v>-0.0182</v>
       </c>
       <c r="S45" t="n">
         <v>301</v>
       </c>
       <c r="T45" t="n">
-        <v>0.0589</v>
+        <v>0.0607</v>
       </c>
       <c r="U45" t="n">
-        <v>0.0578</v>
+        <v>0.057</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -18017,49 +19557,49 @@
       </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="n">
-        <v>0.1238</v>
+        <v>0.1294</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.3867</v>
+        <v>0.4043</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.0579</v>
+        <v>0.0597</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.1238</v>
+        <v>0.1294</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.0616</v>
+        <v>0.0668</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.0733</v>
+        <v>0.079</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.1096</v>
+        <v>0.1153</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.0209</v>
+        <v>0.0208</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.0954</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="AH45" t="n">
-        <v>9.140000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.0053</v>
+        <v>0.0055</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.035858</v>
+        <v>-0.047664</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.401702</v>
+        <v>1.388515</v>
       </c>
       <c r="AM45" t="n">
-        <v>40.17</v>
+        <v>38.85</v>
       </c>
       <c r="AN45" t="n">
         <v>1</v>
@@ -18086,13 +19626,13 @@
         <v>1</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.058282</v>
+        <v>0.058002</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.6153</v>
+        <v>0.8218</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -18102,7 +19642,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -18240,27 +19780,71 @@
         <v>0</v>
       </c>
       <c r="CP45" t="n">
-        <v>0.5101</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="CQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR45" t="inlineStr"/>
-      <c r="CS45" t="inlineStr"/>
-      <c r="CT45" t="inlineStr"/>
-      <c r="CU45" t="inlineStr"/>
-      <c r="CV45" t="inlineStr"/>
-      <c r="CW45" t="inlineStr"/>
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="CS45" t="inlineStr">
+        <is>
+          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
+        </is>
+      </c>
+      <c r="CT45" t="inlineStr">
+        <is>
+          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
+        </is>
+      </c>
+      <c r="CU45" t="inlineStr">
+        <is>
+          <t>OTM extremo sem vol prevista muito forte</t>
+        </is>
+      </c>
+      <c r="CV45" t="inlineStr">
+        <is>
+          <t>~0.45</t>
+        </is>
+      </c>
+      <c r="CW45" t="inlineStr">
+        <is>
+          <t>naked_30: esp=+0.060 | spread_35_20: esp=+0.067 | spread_45_25: esp=+0.079 | spread_45_15: esp=+0.115</t>
+        </is>
+      </c>
       <c r="CX45" t="inlineStr">
         <is>
-          <t>Ticker neutro — sem sinal operacional</t>
-        </is>
-      </c>
-      <c r="CY45" t="inlineStr"/>
-      <c r="CZ45" t="inlineStr"/>
-      <c r="DA45" t="inlineStr"/>
-      <c r="DB45" t="inlineStr"/>
-      <c r="DC45" t="inlineStr"/>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.129 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+        </is>
+      </c>
+      <c r="CY45" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="CZ45" t="inlineStr">
+        <is>
+          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
+        </is>
+      </c>
+      <c r="DA45" t="inlineStr">
+        <is>
+          <t>80% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DB45" t="inlineStr">
+        <is>
+          <t>40% do prêmio pago</t>
+        </is>
+      </c>
+      <c r="DC45" t="inlineStr">
+        <is>
+          <t>Regra 80/40: realizar 80%, stop 40%.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -18269,7 +19853,7 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -18371,13 +19955,13 @@
         <v>-0.0944</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0234</v>
+        <v>0.0203</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.5239</v>
+        <v>0.3531</v>
       </c>
       <c r="AH46" t="n">
-        <v>11.02</v>
+        <v>10.76</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -18386,13 +19970,13 @@
         <v>-0.0074</v>
       </c>
       <c r="AK46" t="n">
-        <v>-0.06615500000000001</v>
+        <v>-0.084219</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.019545</v>
+        <v>1.193239</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.95</v>
+        <v>19.32</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -18422,10 +20006,10 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.06526899999999999</v>
+        <v>0.056575</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.0136</v>
+        <v>1.4886</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -18577,7 +20161,7 @@
         <v>0</v>
       </c>
       <c r="CP46" t="n">
-        <v>0.4743</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="CQ46" t="n">
         <v>0</v>
@@ -18606,7 +20190,7 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -18632,7 +20216,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -18654,13 +20238,13 @@
         <v>1.622</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0257</v>
+        <v>0.0314</v>
       </c>
       <c r="Q47" t="n">
         <v>443</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0398</v>
+        <v>0.0425</v>
       </c>
       <c r="S47" t="n">
         <v>315</v>
@@ -18704,13 +20288,13 @@
         <v>0.2223</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.028</v>
+        <v>0.0278</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5471</v>
       </c>
       <c r="AH47" t="n">
-        <v>6.82</v>
+        <v>6.63</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -18719,13 +20303,13 @@
         <v>0.1415</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.048433</v>
+        <v>-0.06907199999999999</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.933231</v>
+        <v>0.968729</v>
       </c>
       <c r="AM47" t="n">
-        <v>-6.68</v>
+        <v>-3.13</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
@@ -18755,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.078123</v>
+        <v>0.07764500000000001</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.62</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -18768,7 +20352,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -18910,7 +20494,7 @@
         <v>0</v>
       </c>
       <c r="CP47" t="n">
-        <v>0.395</v>
+        <v>0.4231</v>
       </c>
       <c r="CQ47" t="n">
         <v>0</v>
@@ -18939,7 +20523,7 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -18965,7 +20549,7 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -18987,16 +20571,16 @@
         <v>2.4078</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.0804</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q48" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="R48" t="n">
-        <v>-0.0292</v>
+        <v>-0.0289</v>
       </c>
       <c r="S48" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T48" t="n">
         <v>0.1075</v>
@@ -19041,13 +20625,13 @@
         <v>-0.1585</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.0267</v>
+        <v>0.0257</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.1203</v>
+        <v>0.092</v>
       </c>
       <c r="AH48" t="n">
-        <v>7.71</v>
+        <v>7.76</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -19056,13 +20640,13 @@
         <v>0.0021</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.056563</v>
+        <v>-0.024262</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.072504</v>
+        <v>1.104389</v>
       </c>
       <c r="AM48" t="n">
-        <v>7.25</v>
+        <v>10.44</v>
       </c>
       <c r="AN48" t="n">
         <v>1</v>
@@ -19071,7 +20655,7 @@
         <v>1</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ48" t="n">
         <v>0</v>
@@ -19092,10 +20676,10 @@
         <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.07437000000000001</v>
+        <v>0.071718</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.3383</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
@@ -19105,12 +20689,12 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BC48" t="n">
@@ -19243,7 +20827,7 @@
         <v>0</v>
       </c>
       <c r="CP48" t="n">
-        <v>0.5092</v>
+        <v>0.4726</v>
       </c>
       <c r="CQ48" t="n">
         <v>0</v>
@@ -19272,7 +20856,7 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -19323,13 +20907,13 @@
         <v>0.0161</v>
       </c>
       <c r="Q49" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="R49" t="n">
         <v>0.1709</v>
       </c>
       <c r="S49" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T49" t="n">
         <v>-0.18</v>
@@ -19344,7 +20928,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -19374,13 +20958,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0262</v>
+        <v>0.0384</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.5618</v>
+        <v>1</v>
       </c>
       <c r="AH49" t="n">
-        <v>12.26</v>
+        <v>13.53</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -19389,13 +20973,13 @@
         <v>-0.0012</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.057207</v>
+        <v>0.085685</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.041883</v>
+        <v>0.914916</v>
       </c>
       <c r="AM49" t="n">
-        <v>4.19</v>
+        <v>-8.51</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
@@ -19407,7 +20991,7 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR49" t="n">
         <v>1.060061</v>
@@ -19419,16 +21003,16 @@
         <v>0.9672539999999999</v>
       </c>
       <c r="AU49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV49" t="n">
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.072993</v>
+        <v>0.107133</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.7837</v>
+        <v>0.7998</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -19443,7 +21027,7 @@
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
       <c r="BC49" t="n">
@@ -19576,7 +21160,7 @@
         <v>0</v>
       </c>
       <c r="CP49" t="n">
-        <v>0.4552</v>
+        <v>0.3691</v>
       </c>
       <c r="CQ49" t="n">
         <v>0</v>
@@ -19605,7 +21189,7 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -19619,7 +21203,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -19653,7 +21237,7 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0466</v>
+        <v>0.0467</v>
       </c>
       <c r="Q50" t="n">
         <v>443</v>
@@ -19703,13 +21287,13 @@
         <v>0.2287</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.0149</v>
+        <v>0.0155</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.154</v>
+        <v>0.1758</v>
       </c>
       <c r="AH50" t="n">
-        <v>14.01</v>
+        <v>13.75</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -19718,13 +21302,13 @@
         <v>0.0385</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.009523</v>
+        <v>-0.013413</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.030837</v>
+        <v>1.035548</v>
       </c>
       <c r="AM50" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="AN50" t="n">
         <v>1</v>
@@ -19754,10 +21338,10 @@
         <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.041552</v>
+        <v>0.043321</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.2292</v>
+        <v>0.3096</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
@@ -19909,7 +21493,7 @@
         <v>0</v>
       </c>
       <c r="CP50" t="n">
-        <v>0.4383</v>
+        <v>0.4419</v>
       </c>
       <c r="CQ50" t="n">
         <v>0</v>
@@ -38313,7 +39897,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vol_live_sem_expansao</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -38385,7 +39969,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -38421,12 +40005,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -38529,12 +40113,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -38565,7 +40149,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -38709,7 +40293,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -38745,7 +40329,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -38961,7 +40545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -39069,7 +40653,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -39753,7 +41337,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -39825,7 +41409,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -39861,12 +41445,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -39933,7 +41517,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -39969,7 +41553,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -40240,7 +41824,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -40255,15 +41839,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vol_live_sem_expansao</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.4482</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -40325,7 +41909,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.5693</v>
+        <v>0.583</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -40372,7 +41956,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -40387,15 +41971,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.4336</v>
+        <v>0.4567</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -40448,25 +42032,25 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.4719</v>
+        <v>0.482</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
     </row>
@@ -40569,7 +42153,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.5405</v>
+        <v>0.6088</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -40819,7 +42403,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4213</v>
+        <v>0.3922</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -40876,20 +42460,20 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.4931</v>
+        <v>0.5022</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -41024,7 +42608,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -41039,15 +42623,15 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.5006</v>
+        <v>0.4375</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -41185,7 +42769,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -41201,7 +42785,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.4129</v>
+        <v>0.42</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -41210,7 +42794,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
     </row>
@@ -41267,7 +42851,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.5648</v>
+        <v>0.5041</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -41333,7 +42917,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.5322</v>
+        <v>0.5453</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -41380,13 +42964,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -41395,20 +42979,20 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.5003</v>
+        <v>0.4427</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
     </row>
@@ -41446,7 +43030,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -41461,15 +43045,15 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.3226</v>
+        <v>0.2818</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -41573,7 +43157,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.4456</v>
+        <v>0.4642</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -41685,7 +43269,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.4767</v>
+        <v>0.4763</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -41797,7 +43381,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.4657</v>
+        <v>0.4463</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -41850,7 +43434,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -41863,7 +43447,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.406</v>
+        <v>0.4108</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -42021,7 +43605,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.3799</v>
+        <v>0.3979</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -42114,7 +43698,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -42129,15 +43713,15 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.4656</v>
+        <v>0.4725</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -42199,7 +43783,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.5441</v>
+        <v>0.5411</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -42265,7 +43849,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.3642</v>
+        <v>0.3657</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -42327,15 +43911,15 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.4754</v>
+        <v>0.4973</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -42397,7 +43981,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.5573</v>
+        <v>0.5269</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -42647,7 +44231,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.4031</v>
+        <v>0.4123</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -42713,7 +44297,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.4393</v>
+        <v>0.4376</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -42779,7 +44363,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.4516</v>
+        <v>0.4532</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -42845,7 +44429,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.349</v>
+        <v>0.3647</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -43049,7 +44633,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.4616</v>
+        <v>0.4416</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -43115,7 +44699,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.4739</v>
+        <v>0.4927</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -43181,7 +44765,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.3624</v>
+        <v>0.3744</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -43247,7 +44831,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.3861</v>
+        <v>0.3725</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -43313,7 +44897,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.4006</v>
+        <v>0.4058</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -43609,7 +45193,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.4474</v>
+        <v>0.3679</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -43997,7 +45581,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.456</v>
+        <v>0.476</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -44109,7 +45693,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.383</v>
+        <v>0.3926</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -44175,7 +45759,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.4289</v>
+        <v>0.4426</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -44283,7 +45867,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.504</v>
+        <v>0.4859</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -44349,7 +45933,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.4077</v>
+        <v>0.4122</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -44457,7 +46041,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.3735</v>
+        <v>0.3753</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -44569,7 +46153,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.4193</v>
+        <v>0.4116</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -44616,7 +46200,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -44631,15 +46215,15 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.4389</v>
+        <v>0.4462</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -44965,7 +46549,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5596</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -45149,10 +46733,10 @@
         <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -45161,20 +46745,20 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.5994</v>
+        <v>0.3658</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
     </row>
@@ -45222,20 +46806,20 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0.5101</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -45297,7 +46881,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.4743</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -45405,15 +46989,15 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.395</v>
+        <v>0.4231</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -45456,7 +47040,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>1</v>
@@ -45471,20 +47055,20 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0.5092</v>
+        <v>0.4726</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
     </row>
@@ -45571,10 +47155,10 @@
         <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -45587,7 +47171,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.4552</v>
+        <v>0.3691</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -45596,7 +47180,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
     </row>
@@ -45699,7 +47283,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0.4383</v>
+        <v>0.4419</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -45925,7 +47509,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -45935,7 +47519,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -45955,7 +47539,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -45985,7 +47569,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -45995,7 +47579,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -46025,7 +47609,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
@@ -46045,7 +47629,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="32">
@@ -46055,7 +47639,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
